--- a/ig/DM-MARS-2026/ValueSet-JDV-J07-XdsTypeCode-CISIS.xlsx
+++ b/ig/DM-MARS-2026/ValueSet-JDV-J07-XdsTypeCode-CISIS.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="277">
   <si>
     <t>Property</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260202120000</t>
+    <t>20260601120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T12:00:00+01:00</t>
+    <t>2026-06-01T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -338,78 +338,78 @@
     <t>Lettre de liaison à la sortie d'un établissement de soins</t>
   </si>
   <si>
+    <t>11502-2</t>
+  </si>
+  <si>
+    <t>CR d'examens biologiques</t>
+  </si>
+  <si>
+    <t>11505-5</t>
+  </si>
+  <si>
+    <t>CR d'acte thérapeutique (autre)</t>
+  </si>
+  <si>
+    <t>11506-3</t>
+  </si>
+  <si>
+    <t>CR ou fiche de suivi de soins par auxiliaire médical</t>
+  </si>
+  <si>
+    <t>15507-7</t>
+  </si>
+  <si>
+    <t>CR de passage aux urgences</t>
+  </si>
+  <si>
+    <t>15508-5</t>
+  </si>
+  <si>
+    <t>CR d'accouchement</t>
+  </si>
+  <si>
+    <t>18776-5</t>
+  </si>
+  <si>
+    <t>Plan personnalisé de soins</t>
+  </si>
+  <si>
+    <t>18748-4</t>
+  </si>
+  <si>
+    <t>CR d'imagerie médicale</t>
+  </si>
+  <si>
+    <t>18761-7</t>
+  </si>
+  <si>
+    <t>Note de transfert (dont lettre de liaison à l'entrée en établissement de soins)</t>
+  </si>
+  <si>
+    <t>28617-9</t>
+  </si>
+  <si>
+    <t>Bilan bucco-dentaire</t>
+  </si>
+  <si>
+    <t>28653-4</t>
+  </si>
+  <si>
+    <t>Document du secteur social / médico-social</t>
+  </si>
+  <si>
+    <t>29274-8</t>
+  </si>
+  <si>
+    <t>Mesures de signes vitaux</t>
+  </si>
+  <si>
     <t>34112-3</t>
   </si>
   <si>
     <t>CR hospitalier (séjour)</t>
   </si>
   <si>
-    <t>11502-2</t>
-  </si>
-  <si>
-    <t>CR d'examens biologiques</t>
-  </si>
-  <si>
-    <t>11505-5</t>
-  </si>
-  <si>
-    <t>CR d'acte thérapeutique (autre)</t>
-  </si>
-  <si>
-    <t>11506-3</t>
-  </si>
-  <si>
-    <t>CR ou fiche de suivi de soins par auxiliaire médical</t>
-  </si>
-  <si>
-    <t>15507-7</t>
-  </si>
-  <si>
-    <t>CR de passage aux urgences</t>
-  </si>
-  <si>
-    <t>15508-5</t>
-  </si>
-  <si>
-    <t>CR d'accouchement</t>
-  </si>
-  <si>
-    <t>18776-5</t>
-  </si>
-  <si>
-    <t>Plan personnalisé de soins</t>
-  </si>
-  <si>
-    <t>18748-4</t>
-  </si>
-  <si>
-    <t>CR d'imagerie médicale</t>
-  </si>
-  <si>
-    <t>18761-7</t>
-  </si>
-  <si>
-    <t>Note de transfert (dont lettre de liaison à l'entrée en établissement de soins)</t>
-  </si>
-  <si>
-    <t>28617-9</t>
-  </si>
-  <si>
-    <t>Bilan bucco-dentaire</t>
-  </si>
-  <si>
-    <t>28653-4</t>
-  </si>
-  <si>
-    <t>Document du secteur social / médico-social</t>
-  </si>
-  <si>
-    <t>29274-8</t>
-  </si>
-  <si>
-    <t>Mesures de signes vitaux</t>
-  </si>
-  <si>
     <t>34120-6</t>
   </si>
   <si>
@@ -506,6 +506,24 @@
     <t>Notification de rendez-vous</t>
   </si>
   <si>
+    <t>57055-6</t>
+  </si>
+  <si>
+    <t>Synthèse antepartum</t>
+  </si>
+  <si>
+    <t>57057-2</t>
+  </si>
+  <si>
+    <t>Synthèse Salle de Naissance Mère</t>
+  </si>
+  <si>
+    <t>57075-4</t>
+  </si>
+  <si>
+    <t>Synthèse Salle de Naissance Enfant</t>
+  </si>
+  <si>
     <t>57828-6</t>
   </si>
   <si>
@@ -650,6 +668,12 @@
     <t>Planification thérapeutique</t>
   </si>
   <si>
+    <t>78489-2</t>
+  </si>
+  <si>
+    <t>Synthèse Enfant en Maternité</t>
+  </si>
+  <si>
     <t>78513-9</t>
   </si>
   <si>
@@ -716,6 +740,12 @@
     <t>Lettre de liaison à la sortie d'une structure sociale ou médico-sociale</t>
   </si>
   <si>
+    <t>84067-8</t>
+  </si>
+  <si>
+    <t>Synthèse transfusionnelle</t>
+  </si>
+  <si>
     <t>85208-7</t>
   </si>
   <si>
@@ -740,6 +770,18 @@
     <t>Lettre de liaison d'entrée en structure sociale ou médico-sociale</t>
   </si>
   <si>
+    <t>89233-1</t>
+  </si>
+  <si>
+    <t>CR de grossesse</t>
+  </si>
+  <si>
+    <t>89235-6</t>
+  </si>
+  <si>
+    <t>Synthèse Suites de Couches Mère</t>
+  </si>
+  <si>
     <t>89601-9</t>
   </si>
   <si>
@@ -752,6 +794,18 @@
     <t>CR de consultation pharmaceutique</t>
   </si>
   <si>
+    <t>96163-1</t>
+  </si>
+  <si>
+    <t>Bilan de soins infirmiers</t>
+  </si>
+  <si>
+    <t>96173-0</t>
+  </si>
+  <si>
+    <t>Test rapide d'orientation diagnostique</t>
+  </si>
+  <si>
     <t>96349-6</t>
   </si>
   <si>
@@ -764,64 +818,22 @@
     <t>COVID-19 Attestation de vaccination</t>
   </si>
   <si>
-    <t>96173-0</t>
-  </si>
-  <si>
-    <t>Test rapide d'orientation diagnostique</t>
-  </si>
-  <si>
-    <t>57055-6</t>
-  </si>
-  <si>
-    <t>Synthèse antepartum</t>
-  </si>
-  <si>
-    <t>57057-2</t>
-  </si>
-  <si>
-    <t>Synthèse Salle de Naissance Mère</t>
-  </si>
-  <si>
-    <t>57075-4</t>
-  </si>
-  <si>
-    <t>Synthèse Salle de Naissance Enfant</t>
-  </si>
-  <si>
-    <t>89235-6</t>
-  </si>
-  <si>
-    <t>Synthèse Suites de Couches Mère</t>
-  </si>
-  <si>
-    <t>78489-2</t>
-  </si>
-  <si>
-    <t>Synthèse Enfant en Maternité</t>
-  </si>
-  <si>
-    <t>89233-1</t>
-  </si>
-  <si>
-    <t>CR de grossesse</t>
+    <t>97694-4</t>
+  </si>
+  <si>
+    <t>Note d'évaluation en médecine maternelle et fœtale</t>
+  </si>
+  <si>
+    <t>100967-9</t>
+  </si>
+  <si>
+    <t>Rythme cardiaque fœtal</t>
   </si>
   <si>
     <t>101881-1</t>
   </si>
   <si>
     <t>Carte d'implant</t>
-  </si>
-  <si>
-    <t>97694-4</t>
-  </si>
-  <si>
-    <t>Note d'évaluation en médecine maternelle et fœtale</t>
-  </si>
-  <si>
-    <t>100967-9</t>
-  </si>
-  <si>
-    <t>Rythme cardiaque fœtal</t>
   </si>
   <si>
     <t>http://loinc.org</t>
@@ -1413,7 +1425,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B87"/>
+  <dimension ref="A1:B89"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -2102,18 +2114,34 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>98</v>
+        <v>269</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>98</v>
+        <v>270</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="B87" t="s" s="2">
-        <v>269</v>
+      <c r="B89" t="s" s="2">
+        <v>273</v>
       </c>
     </row>
   </sheetData>
@@ -2140,10 +2168,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="3">
@@ -2159,7 +2187,7 @@
         <v>99</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>
